--- a/frontend/public/forms/templates/ris-template.xlsx
+++ b/frontend/public/forms/templates/ris-template.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIO\Desktop\CHERIE\CAPSTONE\frontend\public\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6178036-BE8A-43C8-AD35-7380E6DD8E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBE9DCF-7531-4305-9C51-D0FCBF8DF9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RIS" sheetId="2" r:id="rId1"/>
@@ -694,8 +694,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="8"/>
     </xf>
@@ -708,23 +706,53 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -762,50 +790,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1191,21 +1195,21 @@
   <sheetData>
     <row r="1" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
@@ -1269,236 +1273,236 @@
       <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="48" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="48" t="s">
+      <c r="F10" s="58"/>
+      <c r="G10" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="50"/>
+      <c r="H10" s="58"/>
     </row>
     <row r="11" spans="1:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="38" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="38" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="62"/>
+      <c r="A12" s="52"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="64"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="45"/>
     </row>
     <row r="14" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="64"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="45"/>
     </row>
     <row r="15" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="64"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="45"/>
     </row>
     <row r="16" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="64"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="45"/>
     </row>
     <row r="17" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="72"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="64"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="72"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="64"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="64"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="64"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="64"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="64"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="72"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="64"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="64"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="72"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="64"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="45"/>
     </row>
     <row r="26" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="72"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="64"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="45"/>
     </row>
     <row r="27" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="64"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="45"/>
     </row>
     <row r="28" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="64"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="45"/>
     </row>
     <row r="29" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="72"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="64"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="45"/>
     </row>
     <row r="30" spans="1:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="66"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="47"/>
     </row>
     <row r="31" spans="1:8" ht="0.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
@@ -1512,33 +1516,33 @@
       <c r="A32" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="56"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
-      <c r="B33" s="57"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="58"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="66"/>
     </row>
     <row r="34" spans="1:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="54"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
     </row>
     <row r="35" spans="1:8" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="30"/>
@@ -1546,14 +1550,14 @@
       <c r="C35" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="51" t="s">
+      <c r="E35" s="60"/>
+      <c r="F35" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="52"/>
+      <c r="G35" s="60"/>
       <c r="H35" s="33" t="s">
         <v>22</v>
       </c>
@@ -1564,10 +1568,10 @@
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="25"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="46"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="72"/>
       <c r="H36" s="34"/>
     </row>
     <row r="37" spans="1:8" ht="22.65" customHeight="1" x14ac:dyDescent="0.3">
@@ -1576,11 +1580,11 @@
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="35"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="73"/>
     </row>
     <row r="38" spans="1:8" ht="22.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="28" t="s">
@@ -1588,11 +1592,11 @@
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="35"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="73"/>
     </row>
     <row r="39" spans="1:8" ht="22.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18" t="s">
@@ -1600,11 +1604,11 @@
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="14"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="36"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="39"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
@@ -1613,6 +1617,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="E10:F10"/>
@@ -1622,14 +1634,6 @@
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
